--- a/backend/data/financials_by_company/003005.SZ.xlsx
+++ b/backend/data/financials_by_company/003005.SZ.xlsx
@@ -4167,10 +4167,8 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>102300</t>
-        </is>
+      <c r="D2" t="n">
+        <v>102300</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4379,7 +4377,7 @@
         <v>-8753925</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -4518,7 +4516,7 @@
         </is>
       </c>
       <c r="CZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DA2" t="n">
         <v>-2.4616003</v>
